--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8642,6 +8642,30 @@
         <v>347.4</v>
       </c>
       <c r="F342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="C343" t="n">
+        <v>319.84</v>
+      </c>
+      <c r="D343" t="n">
+        <v>326.52</v>
+      </c>
+      <c r="E343" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="F343" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8658,7 +8682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12201,6 +12225,16 @@
       </c>
       <c r="B354" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -12369,28 +12403,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1329512297829788</v>
+        <v>0.1326539117260619</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06263078485197482</v>
+        <v>0.06275858279284774</v>
       </c>
       <c r="M2" t="n">
-        <v>2.959412302481733</v>
+        <v>2.952069289240405</v>
       </c>
       <c r="N2" t="n">
-        <v>14.50619541570286</v>
+        <v>14.46450314581617</v>
       </c>
       <c r="O2" t="n">
-        <v>3.808699963990714</v>
+        <v>3.803222731554933</v>
       </c>
       <c r="P2" t="n">
-        <v>322.3117154256767</v>
+        <v>322.3149086472055</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12447,28 +12481,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1343647523350053</v>
+        <v>0.132044567902702</v>
       </c>
       <c r="J3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04940660132027996</v>
+        <v>0.04799586201903272</v>
       </c>
       <c r="M3" t="n">
-        <v>3.297776652787308</v>
+        <v>3.298186026991401</v>
       </c>
       <c r="N3" t="n">
-        <v>19.04699640026947</v>
+        <v>19.03536344853758</v>
       </c>
       <c r="O3" t="n">
-        <v>4.364286470921618</v>
+        <v>4.362953523536273</v>
       </c>
       <c r="P3" t="n">
-        <v>320.1344820705312</v>
+        <v>320.1594010510903</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12525,28 +12559,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1353856482423229</v>
+        <v>0.1339819920006756</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05697645602243195</v>
+        <v>0.0561698323474269</v>
       </c>
       <c r="M4" t="n">
-        <v>3.127568067207842</v>
+        <v>3.123834718906644</v>
       </c>
       <c r="N4" t="n">
-        <v>16.63482875429706</v>
+        <v>16.60231470147015</v>
       </c>
       <c r="O4" t="n">
-        <v>4.078581708669947</v>
+        <v>4.074593808156851</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2442549334473</v>
+        <v>325.2593303223304</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12603,28 +12637,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08067072825817184</v>
+        <v>0.08054275603915524</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02293366904619232</v>
+        <v>0.02301263891535521</v>
       </c>
       <c r="M5" t="n">
-        <v>2.924069653053247</v>
+        <v>2.916189444622461</v>
       </c>
       <c r="N5" t="n">
-        <v>15.20296990451535</v>
+        <v>15.1586508151078</v>
       </c>
       <c r="O5" t="n">
-        <v>3.89909860153797</v>
+        <v>3.893411205499338</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5529011525</v>
+        <v>342.55427558515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12662,7 +12696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23609,6 +23643,38 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.459501209877104,174.4330808879455</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.460175734741625,174.4334359615051</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.46079922008528,174.4339103606356</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-35.46137550715122,174.43449510370692</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8668,6 +8668,78 @@
       <c r="F343" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>327</v>
+      </c>
+      <c r="C344" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="D344" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="E344" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="C345" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="D345" t="n">
+        <v>325.98</v>
+      </c>
+      <c r="E345" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>328.49</v>
+      </c>
+      <c r="C346" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="D346" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="E346" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12235,6 +12307,36 @@
       </c>
       <c r="B355" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12403,28 +12505,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1326539117260619</v>
+        <v>0.1364832731171112</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06275858279284774</v>
+        <v>0.06723294427889603</v>
       </c>
       <c r="M2" t="n">
-        <v>2.952069289240405</v>
+        <v>2.946982987065857</v>
       </c>
       <c r="N2" t="n">
-        <v>14.46450314581617</v>
+        <v>14.38443277877962</v>
       </c>
       <c r="O2" t="n">
-        <v>3.803222731554933</v>
+        <v>3.792681476050899</v>
       </c>
       <c r="P2" t="n">
-        <v>322.3149086472055</v>
+        <v>322.2736264064943</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12481,28 +12583,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.132044567902702</v>
+        <v>0.124731811993638</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04799586201903272</v>
+        <v>0.04353391957668185</v>
       </c>
       <c r="M3" t="n">
-        <v>3.298186026991401</v>
+        <v>3.300906613839027</v>
       </c>
       <c r="N3" t="n">
-        <v>19.03536344853758</v>
+        <v>19.02563144652419</v>
       </c>
       <c r="O3" t="n">
-        <v>4.362953523536273</v>
+        <v>4.361838081190565</v>
       </c>
       <c r="P3" t="n">
-        <v>320.1594010510903</v>
+        <v>320.2382069484884</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12559,28 +12661,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1339819920006756</v>
+        <v>0.1280037264968616</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0561698323474269</v>
+        <v>0.05219140111739828</v>
       </c>
       <c r="M4" t="n">
-        <v>3.123834718906644</v>
+        <v>3.119760163205133</v>
       </c>
       <c r="N4" t="n">
-        <v>16.60231470147015</v>
+        <v>16.56188364357095</v>
       </c>
       <c r="O4" t="n">
-        <v>4.074593808156851</v>
+        <v>4.069629423371489</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2593303223304</v>
+        <v>325.3237563838935</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12637,28 +12739,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08054275603915524</v>
+        <v>0.08086182154916166</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02301263891535521</v>
+        <v>0.02363738508922408</v>
       </c>
       <c r="M5" t="n">
-        <v>2.916189444622461</v>
+        <v>2.897861706578647</v>
       </c>
       <c r="N5" t="n">
-        <v>15.1586508151078</v>
+        <v>15.03285838286848</v>
       </c>
       <c r="O5" t="n">
-        <v>3.893411205499338</v>
+        <v>3.877223024649018</v>
       </c>
       <c r="P5" t="n">
-        <v>342.55427558515</v>
+        <v>342.5508262471177</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12696,7 +12798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23675,6 +23777,102 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.4594944443246,174.43309670676683</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.4601823332696,174.43342053316096</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.46080819915283,174.43388936624876</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.46137859764793,174.4344878776996</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.459487135855134,174.43311379499667</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.46017581826731,174.43343576620964</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.46080147529327,174.43390508762727</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.46137191549235,174.43450350149848</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.45948822168502,174.43311125617413</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.46017289486824,174.43344260155115</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.460801433530165,174.43390518527556</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.46137095493232,174.43450574741937</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0080/nzd0080.xlsx
+++ b/data/nzd0080/nzd0080.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F346"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8738,6 +8738,30 @@
         <v>345.59</v>
       </c>
       <c r="F346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="C347" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="D347" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="E347" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="F347" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8754,7 +8778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12337,6 +12361,16 @@
       </c>
       <c r="B358" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -12505,28 +12539,28 @@
         <v>0.1052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1364832731171112</v>
+        <v>0.1385697691087138</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06723294427889603</v>
+        <v>0.06942211088536776</v>
       </c>
       <c r="M2" t="n">
-        <v>2.946982987065857</v>
+        <v>2.949895884397332</v>
       </c>
       <c r="N2" t="n">
-        <v>14.38443277877962</v>
+        <v>14.37956621638007</v>
       </c>
       <c r="O2" t="n">
-        <v>3.792681476050899</v>
+        <v>3.792039848996853</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2736264064943</v>
+        <v>322.2510369857242</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12583,28 +12617,28 @@
         <v>0.1006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.124731811993638</v>
+        <v>0.1237974873746426</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04353391957668185</v>
+        <v>0.04316807230693898</v>
       </c>
       <c r="M3" t="n">
-        <v>3.300906613839027</v>
+        <v>3.295383891308318</v>
       </c>
       <c r="N3" t="n">
-        <v>19.02563144652419</v>
+        <v>18.97800459566743</v>
       </c>
       <c r="O3" t="n">
-        <v>4.361838081190565</v>
+        <v>4.356375167001509</v>
       </c>
       <c r="P3" t="n">
-        <v>320.2382069484884</v>
+        <v>320.2483224014005</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12661,28 +12695,28 @@
         <v>0.1036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1280037264968616</v>
+        <v>0.1272520455984136</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05219140111739828</v>
+        <v>0.05192178338566367</v>
       </c>
       <c r="M4" t="n">
-        <v>3.119760163205133</v>
+        <v>3.113659196684558</v>
       </c>
       <c r="N4" t="n">
-        <v>16.56188364357095</v>
+        <v>16.51878101976892</v>
       </c>
       <c r="O4" t="n">
-        <v>4.069629423371489</v>
+        <v>4.064330328574306</v>
       </c>
       <c r="P4" t="n">
-        <v>325.3237563838935</v>
+        <v>325.3318944470233</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12739,28 +12773,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08086182154916166</v>
+        <v>0.08203558576225081</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02363738508922408</v>
+        <v>0.02445044592338153</v>
       </c>
       <c r="M5" t="n">
-        <v>2.897861706578647</v>
+        <v>2.89483581280534</v>
       </c>
       <c r="N5" t="n">
-        <v>15.03285838286848</v>
+        <v>15.00102730289045</v>
       </c>
       <c r="O5" t="n">
-        <v>3.877223024649018</v>
+        <v>3.873115968169615</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5508262471177</v>
+        <v>342.5381185046629</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12798,7 +12832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F346"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23873,6 +23907,38 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.45948379483971,174.43312160675785</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.46016667220325,174.43345715106216</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.46079512729982,174.43391993016849</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.46136611036809,174.43451707467165</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
